--- a/artfynd/A 2085-2023 artfynd.xlsx
+++ b/artfynd/A 2085-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 2085-2023 artfynd.xlsx
+++ b/artfynd/A 2085-2023 artfynd.xlsx
@@ -1353,10 +1353,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119645372</v>
+        <v>119645812</v>
       </c>
       <c r="B8" t="n">
-        <v>94681</v>
+        <v>56621</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1369,24 +1369,32 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>100038</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gotland, Gtl</t>
@@ -1396,10 +1404,10 @@
         <v>721922</v>
       </c>
       <c r="R8" t="n">
-        <v>6397801</v>
+        <v>6397795</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1423,12 +1431,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-09-22</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-09-22</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1455,10 +1463,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119645812</v>
+        <v>119645372</v>
       </c>
       <c r="B9" t="n">
-        <v>56621</v>
+        <v>94681</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1471,32 +1479,24 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100038</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gotland, Gtl</t>
@@ -1506,10 +1506,10 @@
         <v>721922</v>
       </c>
       <c r="R9" t="n">
-        <v>6397795</v>
+        <v>6397801</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1533,12 +1533,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2023-09-22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2023-09-22</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 2085-2023 artfynd.xlsx
+++ b/artfynd/A 2085-2023 artfynd.xlsx
@@ -1353,10 +1353,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119645812</v>
+        <v>119645372</v>
       </c>
       <c r="B8" t="n">
-        <v>56621</v>
+        <v>94681</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1369,32 +1369,24 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100038</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gotland, Gtl</t>
@@ -1404,10 +1396,10 @@
         <v>721922</v>
       </c>
       <c r="R8" t="n">
-        <v>6397795</v>
+        <v>6397801</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1431,12 +1423,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2023-09-22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2023-09-22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1463,10 +1455,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119645372</v>
+        <v>119645812</v>
       </c>
       <c r="B9" t="n">
-        <v>94681</v>
+        <v>56621</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1479,24 +1471,32 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2180</v>
+        <v>100038</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gotland, Gtl</t>
@@ -1506,10 +1506,10 @@
         <v>721922</v>
       </c>
       <c r="R9" t="n">
-        <v>6397801</v>
+        <v>6397795</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1533,12 +1533,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-09-22</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-09-22</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 2085-2023 artfynd.xlsx
+++ b/artfynd/A 2085-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>106165810</v>
+        <v>106165690</v>
       </c>
       <c r="B2" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,12 +705,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -723,14 +718,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Västers, Gtl</t>
+          <t>Västers, Västers kanal, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>721918.5873614969</v>
+        <v>721966</v>
       </c>
       <c r="R2" t="n">
-        <v>6397770.984114291</v>
+        <v>6397770</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -760,19 +755,9 @@
           <t>2023-01-26</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-01-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,15 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>106165687</v>
+        <v>106165810</v>
       </c>
       <c r="B3" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,31 +796,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219798</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -852,13 +832,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>721930.2039353262</v>
+        <v>721918</v>
       </c>
       <c r="R3" t="n">
-        <v>6397794.134497659</v>
+        <v>6397771</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,19 +865,9 @@
           <t>2023-01-26</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-01-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,15 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112363550</v>
+        <v>112363369</v>
       </c>
       <c r="B4" t="n">
-        <v>5182</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -941,27 +906,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105930</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -970,10 +935,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>721928</v>
+        <v>721921</v>
       </c>
       <c r="R4" t="n">
-        <v>6397835</v>
+        <v>6397800</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1032,15 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112363369</v>
+        <v>112363370</v>
       </c>
       <c r="B5" t="n">
-        <v>93661</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1077,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>721921</v>
+        <v>721855</v>
       </c>
       <c r="R5" t="n">
-        <v>6397800</v>
+        <v>6397732</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1139,15 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112363391</v>
+        <v>119645372</v>
       </c>
       <c r="B6" t="n">
-        <v>73866</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1155,39 +1110,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6426</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Suderskog, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>721924</v>
+        <v>721922</v>
       </c>
       <c r="R6" t="n">
-        <v>6397845</v>
+        <v>6397801</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1246,15 +1196,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112363523</v>
+        <v>119645373</v>
       </c>
       <c r="B7" t="n">
-        <v>85350</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,39 +1207,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3712</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Suderskog, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>721925</v>
+        <v>721856</v>
       </c>
       <c r="R7" t="n">
-        <v>6397844</v>
+        <v>6397732</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1353,50 +1293,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119645372</v>
+        <v>112363523</v>
       </c>
       <c r="B8" t="n">
-        <v>94681</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87170</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>3712</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Suderskog, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>721922</v>
+        <v>721925</v>
       </c>
       <c r="R8" t="n">
-        <v>6397801</v>
+        <v>6397844</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,61 +1395,53 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119645812</v>
+        <v>112363391</v>
       </c>
       <c r="B9" t="n">
-        <v>56621</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100038</v>
+        <v>6426</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Suderskog, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>721922</v>
+        <v>721923</v>
       </c>
       <c r="R9" t="n">
-        <v>6397795</v>
+        <v>6397845</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1533,12 +1465,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2023-09-22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2023-09-22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1562,6 +1494,634 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>119645812</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57247</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100038</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Skogsduva</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Columba oenas</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Gotland, Gtl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>721922</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6397795</v>
+      </c>
+      <c r="S10" t="n">
+        <v>50</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Bäl</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-04-30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-04-30</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>112363550</v>
+      </c>
+      <c r="B11" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Suderskog, Gtl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>721929</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6397835</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Bäl</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-09-22</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-09-22</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>112363585</v>
+      </c>
+      <c r="B12" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Suderskog, Gtl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>721947</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6397876</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Bäl</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-09-22</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-09-22</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>kläckhål</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>112363586</v>
+      </c>
+      <c r="B13" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Suderskog, Gtl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>721925</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6397866</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Bäl</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-09-22</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-09-22</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>kläckhål</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>106165687</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Västers, Gtl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>721930</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6397795</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Bäl</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2023-01-26</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2023-01-26</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Elina  Ambjörnsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Elina  Ambjörnsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>112363297</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Suderskog, Gtl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>721961</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6397745</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Bäl</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2023-09-22</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2023-09-22</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2085-2023 artfynd.xlsx
+++ b/artfynd/A 2085-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106165690</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106165810</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -994,6 +1009,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112363369</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112363370</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1193,6 +1218,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119645372</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1290,6 +1320,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119645373</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1392,6 +1427,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112363523</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1494,6 +1534,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112363391</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1599,6 +1644,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119645812</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1701,6 +1751,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112363550</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1808,6 +1863,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112363585</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1915,6 +1975,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112363586</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2025,6 +2090,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106165687</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2122,8 +2192,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112363297</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>